--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/panel_11/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/panel_11/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,23 +454,28 @@
           <t>Unit 7</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
       <c r="C2" t="n">
-        <v>17.84545</v>
+        <v>17.85291</v>
       </c>
       <c r="D2" t="n">
-        <v>17.46086</v>
+        <v>17.55576</v>
       </c>
       <c r="E2" t="n">
-        <v>17.32605</v>
+        <v>17.58184</v>
       </c>
       <c r="F2" t="n">
-        <v>45.21258</v>
+        <v>43.98313</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05322</v>
+        <v>0.05248</v>
       </c>
       <c r="H2" t="n">
-        <v>1.89081</v>
+        <v>1.90161</v>
       </c>
     </row>
     <row r="3">
@@ -480,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.63962</v>
+        <v>17.66951</v>
       </c>
       <c r="D3" t="n">
-        <v>17.23141</v>
+        <v>17.25065</v>
       </c>
       <c r="E3" t="n">
-        <v>17.34487</v>
+        <v>17.42245</v>
       </c>
       <c r="F3" t="n">
-        <v>44.41799</v>
+        <v>44.90319</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05261</v>
+        <v>0.05298</v>
       </c>
       <c r="H3" t="n">
-        <v>1.88526</v>
+        <v>1.9164</v>
       </c>
     </row>
     <row r="4">
@@ -505,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.57101</v>
+        <v>17.69035</v>
       </c>
       <c r="D4" t="n">
-        <v>17.55458</v>
+        <v>17.20875</v>
       </c>
       <c r="E4" t="n">
-        <v>17.78256</v>
+        <v>17.65975</v>
       </c>
       <c r="F4" t="n">
-        <v>45.14711</v>
+        <v>44.11978</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05264</v>
+        <v>0.05395</v>
       </c>
       <c r="H4" t="n">
-        <v>1.94479</v>
+        <v>1.92136</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.30013</v>
+        <v>17.63964</v>
       </c>
       <c r="D5" t="n">
-        <v>17.22211</v>
+        <v>17.43189</v>
       </c>
       <c r="E5" t="n">
-        <v>17.53767</v>
+        <v>17.53853</v>
       </c>
       <c r="F5" t="n">
-        <v>44.78034</v>
+        <v>44.58759</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05348</v>
+        <v>0.05304</v>
       </c>
       <c r="H5" t="n">
-        <v>1.92009</v>
+        <v>1.93805</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.23088</v>
+        <v>18.00927</v>
       </c>
       <c r="D6" t="n">
-        <v>17.25718</v>
+        <v>17.26533</v>
       </c>
       <c r="E6" t="n">
-        <v>17.6718</v>
+        <v>17.98195</v>
       </c>
       <c r="F6" t="n">
-        <v>44.60166</v>
+        <v>45.03526</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05236</v>
+        <v>0.05357</v>
       </c>
       <c r="H6" t="n">
-        <v>1.91886</v>
+        <v>1.9233</v>
       </c>
     </row>
     <row r="7">
@@ -580,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.508</v>
+        <v>17.84967</v>
       </c>
       <c r="D7" t="n">
-        <v>17.34865</v>
+        <v>17.14702</v>
       </c>
       <c r="E7" t="n">
-        <v>17.44247</v>
+        <v>17.37374</v>
       </c>
       <c r="F7" t="n">
-        <v>44.42468</v>
+        <v>44.17143</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0536</v>
+        <v>0.05342</v>
       </c>
       <c r="H7" t="n">
-        <v>1.90066</v>
+        <v>1.86033</v>
       </c>
     </row>
     <row r="8">
@@ -605,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.42225</v>
+        <v>17.58103</v>
       </c>
       <c r="D8" t="n">
-        <v>16.99946</v>
+        <v>17.18303</v>
       </c>
       <c r="E8" t="n">
-        <v>17.76293</v>
+        <v>17.55033</v>
       </c>
       <c r="F8" t="n">
-        <v>44.74986</v>
+        <v>44.01655</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05377</v>
+        <v>0.05331</v>
       </c>
       <c r="H8" t="n">
-        <v>1.87677</v>
+        <v>1.89964</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18.0222</v>
+        <v>17.84762</v>
       </c>
       <c r="D9" t="n">
-        <v>17.33137</v>
+        <v>17.33314</v>
       </c>
       <c r="E9" t="n">
-        <v>17.47698</v>
+        <v>17.60566</v>
       </c>
       <c r="F9" t="n">
-        <v>45.36366</v>
+        <v>44.91782</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05234</v>
+        <v>0.05294</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8907</v>
+        <v>1.87619</v>
       </c>
     </row>
     <row r="10">
@@ -655,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.55099</v>
+        <v>17.6504</v>
       </c>
       <c r="D10" t="n">
-        <v>17.12445</v>
+        <v>17.51805</v>
       </c>
       <c r="E10" t="n">
-        <v>17.66344</v>
+        <v>17.52222</v>
       </c>
       <c r="F10" t="n">
-        <v>44.46228</v>
+        <v>43.59218</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05365</v>
+        <v>0.05322</v>
       </c>
       <c r="H10" t="n">
-        <v>1.89075</v>
+        <v>1.91853</v>
       </c>
     </row>
     <row r="11">
@@ -713,26 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.55887</v>
+        <v>17.61344</v>
       </c>
       <c r="D12" t="n">
-        <v>17.3994</v>
+        <v>17.28671</v>
       </c>
       <c r="E12" t="n">
-        <v>17.35447</v>
+        <v>17.54927</v>
       </c>
       <c r="F12" t="n">
-        <v>43.83329</v>
+        <v>44.09578</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05241</v>
+        <v>0.05229</v>
       </c>
       <c r="H12" t="n">
-        <v>1.88783</v>
+        <v>1.94112</v>
       </c>
     </row>
     <row r="13">
@@ -742,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.57515</v>
+        <v>17.78706</v>
       </c>
       <c r="D13" t="n">
-        <v>16.79903</v>
+        <v>17.39332</v>
       </c>
       <c r="E13" t="n">
-        <v>17.4023</v>
+        <v>17.62579</v>
       </c>
       <c r="F13" t="n">
-        <v>46.03865</v>
+        <v>44.60654</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05373</v>
+        <v>0.05371</v>
       </c>
       <c r="H13" t="n">
-        <v>1.90424</v>
+        <v>1.90154</v>
       </c>
     </row>
     <row r="14">
@@ -767,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.86764</v>
+        <v>17.69277</v>
       </c>
       <c r="D14" t="n">
-        <v>17.05666</v>
+        <v>17.35713</v>
       </c>
       <c r="E14" t="n">
-        <v>17.21949</v>
+        <v>17.45236</v>
       </c>
       <c r="F14" t="n">
-        <v>44.25724</v>
+        <v>44.66298</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05271</v>
+        <v>0.05305</v>
       </c>
       <c r="H14" t="n">
-        <v>1.91947</v>
+        <v>1.89595</v>
       </c>
     </row>
     <row r="15">
@@ -792,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.61746</v>
+        <v>17.76289</v>
       </c>
       <c r="D15" t="n">
-        <v>17.36339</v>
+        <v>17.23111</v>
       </c>
       <c r="E15" t="n">
-        <v>17.48727</v>
+        <v>17.49737</v>
       </c>
       <c r="F15" t="n">
-        <v>44.41801</v>
+        <v>45.02625</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05426</v>
+        <v>0.05167</v>
       </c>
       <c r="H15" t="n">
-        <v>1.86488</v>
+        <v>1.935</v>
       </c>
     </row>
     <row r="16">
@@ -817,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.92548</v>
+        <v>17.7371</v>
       </c>
       <c r="D16" t="n">
-        <v>17.33354</v>
+        <v>17.18024</v>
       </c>
       <c r="E16" t="n">
-        <v>17.67117</v>
+        <v>17.53069</v>
       </c>
       <c r="F16" t="n">
-        <v>44.56102</v>
+        <v>43.80752</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05263</v>
+        <v>0.05247</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8914</v>
+        <v>1.88206</v>
       </c>
     </row>
     <row r="17">
@@ -842,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.79744</v>
+        <v>17.61403</v>
       </c>
       <c r="D17" t="n">
-        <v>17.18808</v>
+        <v>17.49446</v>
       </c>
       <c r="E17" t="n">
-        <v>17.807</v>
+        <v>17.54157</v>
       </c>
       <c r="F17" t="n">
-        <v>45.13287</v>
+        <v>43.95572</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05336</v>
+        <v>0.05301</v>
       </c>
       <c r="H17" t="n">
-        <v>1.94268</v>
+        <v>1.90235</v>
       </c>
     </row>
     <row r="18">
@@ -867,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.29396</v>
+        <v>18.02083</v>
       </c>
       <c r="D18" t="n">
-        <v>17.26874</v>
+        <v>17.22344</v>
       </c>
       <c r="E18" t="n">
-        <v>17.59239</v>
+        <v>17.53522</v>
       </c>
       <c r="F18" t="n">
-        <v>43.78813</v>
+        <v>45.05299</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05353</v>
+        <v>0.05203</v>
       </c>
       <c r="H18" t="n">
-        <v>1.91967</v>
+        <v>1.90686</v>
       </c>
     </row>
     <row r="19">
@@ -892,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.74198</v>
+        <v>17.56906</v>
       </c>
       <c r="D19" t="n">
-        <v>17.27158</v>
+        <v>17.36308</v>
       </c>
       <c r="E19" t="n">
-        <v>17.48797</v>
+        <v>17.39613</v>
       </c>
       <c r="F19" t="n">
-        <v>43.64656</v>
+        <v>44.4068</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05396</v>
+        <v>0.05325</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9062</v>
+        <v>1.91818</v>
       </c>
     </row>
     <row r="20">
@@ -917,63 +922,43 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.23067</v>
+        <v>17.68142</v>
       </c>
       <c r="D20" t="n">
-        <v>17.45535</v>
+        <v>17.35207</v>
       </c>
       <c r="E20" t="n">
-        <v>17.21902</v>
+        <v>17.55488</v>
       </c>
       <c r="F20" t="n">
-        <v>44.87054</v>
+        <v>43.47894</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05343</v>
+        <v>0.05396</v>
       </c>
       <c r="H20" t="n">
-        <v>1.88237</v>
+        <v>1.92063</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -985,32 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.76928</v>
+        <v>16.42481</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08398</v>
+        <v>16.21103</v>
       </c>
       <c r="E22" t="n">
-        <v>0.64196</v>
+        <v>16.26973</v>
       </c>
       <c r="F22" t="n">
-        <v>1.01277</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.11426</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.007849999999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09739</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.13201</v>
+        <v>262.69047</v>
       </c>
     </row>
     <row r="23">
@@ -1020,28 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.78951</v>
+        <v>16.58856</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08441</v>
+        <v>16.27244</v>
       </c>
       <c r="E23" t="n">
-        <v>0.64198</v>
+        <v>16.27979</v>
       </c>
       <c r="F23" t="n">
-        <v>1.01816</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.1158</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.007990000000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09813</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.13435</v>
+        <v>263.9235</v>
       </c>
     </row>
     <row r="24">
@@ -1051,28 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.76273</v>
+        <v>16.50173</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08328000000000001</v>
+        <v>16.03742</v>
       </c>
       <c r="E24" t="n">
-        <v>0.632</v>
+        <v>16.06791</v>
       </c>
       <c r="F24" t="n">
-        <v>0.99253</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.11344</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00787</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09837</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.13552</v>
+        <v>263.70241</v>
       </c>
     </row>
     <row r="25">
@@ -1082,28 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.78089</v>
+        <v>16.49002</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08474</v>
+        <v>16.19412</v>
       </c>
       <c r="E25" t="n">
-        <v>0.65215</v>
+        <v>16.39905</v>
       </c>
       <c r="F25" t="n">
-        <v>0.99556</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.1146</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.007990000000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09795</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.13343</v>
+        <v>264.36534</v>
       </c>
     </row>
     <row r="26">
@@ -1113,28 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.78892</v>
+        <v>16.42504</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08518000000000001</v>
+        <v>16.40996</v>
       </c>
       <c r="E26" t="n">
-        <v>0.63519</v>
+        <v>16.41013</v>
       </c>
       <c r="F26" t="n">
-        <v>1.01458</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.11185</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09679</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.13139</v>
+        <v>270.1846</v>
       </c>
     </row>
     <row r="27">
@@ -1144,28 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7729200000000001</v>
+        <v>16.35014</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08627</v>
+        <v>16.21724</v>
       </c>
       <c r="E27" t="n">
-        <v>0.63114</v>
+        <v>16.32921</v>
       </c>
       <c r="F27" t="n">
-        <v>0.99679</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.11667</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00792</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09682</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.13161</v>
+        <v>263.19357</v>
       </c>
     </row>
     <row r="28">
@@ -1175,28 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.79042</v>
+        <v>16.36839</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08376</v>
+        <v>15.98918</v>
       </c>
       <c r="E28" t="n">
-        <v>0.61791</v>
+        <v>16.34074</v>
       </c>
       <c r="F28" t="n">
-        <v>1.02574</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.11387</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00801</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09622</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.13247</v>
+        <v>266.52299</v>
       </c>
     </row>
     <row r="29">
@@ -1206,28 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.76888</v>
+        <v>16.3873</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08412</v>
+        <v>16.20359</v>
       </c>
       <c r="E29" t="n">
-        <v>0.64885</v>
+        <v>16.31037</v>
       </c>
       <c r="F29" t="n">
-        <v>1.00045</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.11596</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00791</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09768</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.13129</v>
+        <v>270.43724</v>
       </c>
     </row>
     <row r="30">
@@ -1237,28 +1126,1070 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.78828</v>
+        <v>16.44926</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08576</v>
+        <v>16.41503</v>
       </c>
       <c r="E30" t="n">
-        <v>0.63897</v>
+        <v>16.43331</v>
       </c>
       <c r="F30" t="n">
-        <v>1.01002</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.11657</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00777</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09889000000000001</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.13326</v>
+        <v>266.43154</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>17.4759</v>
+      </c>
+      <c r="D32" t="n">
+        <v>17.14438</v>
+      </c>
+      <c r="E32" t="n">
+        <v>17.2975</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22.72313</v>
+      </c>
+      <c r="G32" t="n">
+        <v>35.92538</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.41484</v>
+      </c>
+      <c r="D33" t="n">
+        <v>17.24832</v>
+      </c>
+      <c r="E33" t="n">
+        <v>17.26427</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22.59839</v>
+      </c>
+      <c r="G33" t="n">
+        <v>35.45262</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17.41265</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.65194</v>
+      </c>
+      <c r="E34" t="n">
+        <v>17.07887</v>
+      </c>
+      <c r="F34" t="n">
+        <v>22.94226</v>
+      </c>
+      <c r="G34" t="n">
+        <v>35.38622</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.78488</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.65969</v>
+      </c>
+      <c r="E35" t="n">
+        <v>17.14816</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22.45682</v>
+      </c>
+      <c r="G35" t="n">
+        <v>35.62787</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17.63237</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.72259</v>
+      </c>
+      <c r="E36" t="n">
+        <v>17.14644</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22.68705</v>
+      </c>
+      <c r="G36" t="n">
+        <v>36.35558</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.50177</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.61458</v>
+      </c>
+      <c r="E37" t="n">
+        <v>17.27846</v>
+      </c>
+      <c r="F37" t="n">
+        <v>22.91857</v>
+      </c>
+      <c r="G37" t="n">
+        <v>36.58429</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>17.44395</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.67909</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.75278</v>
+      </c>
+      <c r="F38" t="n">
+        <v>23.22411</v>
+      </c>
+      <c r="G38" t="n">
+        <v>35.18891</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>17.38005</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.84949</v>
+      </c>
+      <c r="E39" t="n">
+        <v>17.07077</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.59477</v>
+      </c>
+      <c r="G39" t="n">
+        <v>35.86225</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>17.53312</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.8034</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.9641</v>
+      </c>
+      <c r="F40" t="n">
+        <v>23.14628</v>
+      </c>
+      <c r="G40" t="n">
+        <v>35.5208</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>17.66761</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.82475</v>
+      </c>
+      <c r="E42" t="n">
+        <v>17.19411</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.86604</v>
+      </c>
+      <c r="G42" t="n">
+        <v>35.75139</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>17.52683</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.40882</v>
+      </c>
+      <c r="E43" t="n">
+        <v>17.23109</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.73431</v>
+      </c>
+      <c r="G43" t="n">
+        <v>36.40474</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>17.60037</v>
+      </c>
+      <c r="D44" t="n">
+        <v>17.04345</v>
+      </c>
+      <c r="E44" t="n">
+        <v>17.38951</v>
+      </c>
+      <c r="F44" t="n">
+        <v>23.37164</v>
+      </c>
+      <c r="G44" t="n">
+        <v>36.28068</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>17.52994</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.82411</v>
+      </c>
+      <c r="E45" t="n">
+        <v>17.3177</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22.59124</v>
+      </c>
+      <c r="G45" t="n">
+        <v>36.32037</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>17.52596</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.69396</v>
+      </c>
+      <c r="E46" t="n">
+        <v>17.2747</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.87261</v>
+      </c>
+      <c r="G46" t="n">
+        <v>35.0468</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>17.8241</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.43162</v>
+      </c>
+      <c r="E47" t="n">
+        <v>17.21664</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22.87639</v>
+      </c>
+      <c r="G47" t="n">
+        <v>35.85808</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>17.39304</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.79813</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.9451</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.80985</v>
+      </c>
+      <c r="G48" t="n">
+        <v>35.59682</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>17.52882</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.98543</v>
+      </c>
+      <c r="E49" t="n">
+        <v>17.24792</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22.57636</v>
+      </c>
+      <c r="G49" t="n">
+        <v>36.38536</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>17.56178</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.59712</v>
+      </c>
+      <c r="E50" t="n">
+        <v>17.21457</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.58995</v>
+      </c>
+      <c r="G50" t="n">
+        <v>35.5307</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.63454</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.15739</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.62842</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.16434</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.64224</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.1855</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.64496</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.15803</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6482599999999999</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.14639</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.63008</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.16918</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.63972</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.1765</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.64003</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.14181</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.63136</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.17812</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.63717</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.15197</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.63962</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.16017</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.63471</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.16283</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.63464</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.17915</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.6335499999999999</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.15449</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.62193</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.1842</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.63928</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.18302</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.62559</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.19424</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.63407</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.16513</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.79926</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.08375</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.63023</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.00442</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.11277</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.008030000000000001</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09739</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.13411</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.7773099999999999</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.08462</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.63656</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.11271</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.007860000000000001</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09649000000000001</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.13234</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.75801</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.08437</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.65769</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.02096</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.11425</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.008070000000000001</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09568</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.13045</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.77977</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08434</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.6398200000000001</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.00823</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.11434</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.13564</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.76667</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08638999999999999</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.63415</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.01743</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.11459</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09667000000000001</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.13402</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.77556</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08634</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.64476</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.01378</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.11656</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09687</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.13328</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.77151</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08565</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.63989</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.01535</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.11374</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09561</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.13489</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.78366</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08304</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.63861</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.11538</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.008019999999999999</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09621</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.12995</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.77678</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.08559</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.63964</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.00507</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.11302</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.007939999999999999</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09716</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.13336</v>
       </c>
     </row>
   </sheetData>
